--- a/output/yearly_population_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_17_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4218</v>
+        <v>6371</v>
       </c>
       <c r="C2" t="n">
-        <v>10519</v>
+        <v>14534</v>
       </c>
       <c r="D2" t="n">
-        <v>28931</v>
+        <v>30227</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2843</v>
+        <v>3634</v>
       </c>
       <c r="C3" t="n">
-        <v>7928</v>
+        <v>7790</v>
       </c>
       <c r="D3" t="n">
-        <v>14791</v>
+        <v>14421</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2129</v>
+        <v>2976</v>
       </c>
       <c r="C4" t="n">
-        <v>6477</v>
+        <v>4586</v>
       </c>
       <c r="D4" t="n">
-        <v>7923</v>
+        <v>6697</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1487</v>
+        <v>2011</v>
       </c>
       <c r="C5" t="n">
-        <v>5569</v>
+        <v>4487</v>
       </c>
       <c r="D5" t="n">
-        <v>3020</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>899</v>
+        <v>1181</v>
       </c>
       <c r="C6" t="n">
-        <v>3682</v>
+        <v>3741</v>
       </c>
       <c r="D6" t="n">
-        <v>1173</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>414</v>
+        <v>558</v>
       </c>
       <c r="C7" t="n">
-        <v>1978</v>
+        <v>2475</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="C8" t="n">
-        <v>901</v>
+        <v>1192</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>472</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5124</v>
+        <v>7722</v>
       </c>
       <c r="C2" t="n">
-        <v>17292</v>
+        <v>9520</v>
       </c>
       <c r="D2" t="n">
-        <v>25215</v>
+        <v>23877</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2803</v>
+        <v>3896</v>
       </c>
       <c r="C3" t="n">
-        <v>7996</v>
+        <v>9469</v>
       </c>
       <c r="D3" t="n">
-        <v>15630</v>
+        <v>15498</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2075</v>
+        <v>2785</v>
       </c>
       <c r="C4" t="n">
-        <v>6948</v>
+        <v>5967</v>
       </c>
       <c r="D4" t="n">
-        <v>8661</v>
+        <v>7615</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1559</v>
+        <v>2159</v>
       </c>
       <c r="C5" t="n">
-        <v>5809</v>
+        <v>4394</v>
       </c>
       <c r="D5" t="n">
-        <v>3681</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1045</v>
+        <v>1385</v>
       </c>
       <c r="C6" t="n">
-        <v>4479</v>
+        <v>3991</v>
       </c>
       <c r="D6" t="n">
-        <v>1411</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>555</v>
+        <v>727</v>
       </c>
       <c r="C7" t="n">
-        <v>2692</v>
+        <v>3019</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="C8" t="n">
-        <v>1354</v>
+        <v>1707</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>585</v>
+        <v>761</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5153</v>
+        <v>8247</v>
       </c>
       <c r="C2" t="n">
-        <v>11355</v>
+        <v>15926</v>
       </c>
       <c r="D2" t="n">
-        <v>26607</v>
+        <v>25985</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3045</v>
+        <v>4348</v>
       </c>
       <c r="C3" t="n">
-        <v>10385</v>
+        <v>8456</v>
       </c>
       <c r="D3" t="n">
-        <v>15779</v>
+        <v>15511</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2008</v>
+        <v>2737</v>
       </c>
       <c r="C4" t="n">
-        <v>7179</v>
+        <v>7231</v>
       </c>
       <c r="D4" t="n">
-        <v>9401</v>
+        <v>8518</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1569</v>
+        <v>2147</v>
       </c>
       <c r="C5" t="n">
-        <v>6158</v>
+        <v>4894</v>
       </c>
       <c r="D5" t="n">
-        <v>4203</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1136</v>
+        <v>1535</v>
       </c>
       <c r="C6" t="n">
-        <v>4920</v>
+        <v>4115</v>
       </c>
       <c r="D6" t="n">
-        <v>1683</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>667</v>
+        <v>879</v>
       </c>
       <c r="C7" t="n">
-        <v>3365</v>
+        <v>3359</v>
       </c>
       <c r="D7" t="n">
-        <v>799</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>310</v>
+        <v>409</v>
       </c>
       <c r="C8" t="n">
-        <v>1864</v>
+        <v>2178</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="C9" t="n">
-        <v>857</v>
+        <v>1096</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>384</v>
+        <v>472</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1674,7 +1674,7 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4828</v>
+        <v>7606</v>
       </c>
       <c r="C2" t="n">
-        <v>7903</v>
+        <v>11084</v>
       </c>
       <c r="D2" t="n">
-        <v>22042</v>
+        <v>21532</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3604</v>
+        <v>5036</v>
       </c>
       <c r="C3" t="n">
-        <v>14182</v>
+        <v>12897</v>
       </c>
       <c r="D3" t="n">
-        <v>17278</v>
+        <v>16762</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1449</v>
+        <v>1983</v>
       </c>
       <c r="C4" t="n">
-        <v>9771</v>
+        <v>8516</v>
       </c>
       <c r="D4" t="n">
-        <v>9042</v>
+        <v>7976</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1049</v>
+        <v>1418</v>
       </c>
       <c r="C5" t="n">
-        <v>4821</v>
+        <v>4032</v>
       </c>
       <c r="D5" t="n">
-        <v>2779</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>616</v>
+        <v>812</v>
       </c>
       <c r="C6" t="n">
-        <v>3297</v>
+        <v>3291</v>
       </c>
       <c r="D6" t="n">
-        <v>783</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>1826</v>
+        <v>2134</v>
       </c>
       <c r="D7" t="n">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>839</v>
+        <v>1074</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>376</v>
+        <v>462</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1971,7 +1971,7 @@
         <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2962</v>
+        <v>4617</v>
       </c>
       <c r="C2" t="n">
-        <v>4532</v>
+        <v>5487</v>
       </c>
       <c r="D2" t="n">
-        <v>15419</v>
+        <v>15490</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3563</v>
+        <v>5247</v>
       </c>
       <c r="C3" t="n">
-        <v>10377</v>
+        <v>10995</v>
       </c>
       <c r="D3" t="n">
-        <v>17096</v>
+        <v>16433</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1951</v>
+        <v>2699</v>
       </c>
       <c r="C4" t="n">
-        <v>11933</v>
+        <v>10642</v>
       </c>
       <c r="D4" t="n">
-        <v>10039</v>
+        <v>9151</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1149</v>
+        <v>1558</v>
       </c>
       <c r="C5" t="n">
-        <v>6854</v>
+        <v>5906</v>
       </c>
       <c r="D5" t="n">
-        <v>3556</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>717</v>
+        <v>952</v>
       </c>
       <c r="C6" t="n">
-        <v>4010</v>
+        <v>3702</v>
       </c>
       <c r="D6" t="n">
-        <v>969</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>268</v>
+        <v>348</v>
       </c>
       <c r="C7" t="n">
-        <v>2343</v>
+        <v>2616</v>
       </c>
       <c r="D7" t="n">
-        <v>505</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>1385</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>498</v>
       </c>
       <c r="D9" t="n">
         <v>256</v>
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>208</v>
@@ -2156,7 +2156,7 @@
         <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2268,7 +2268,7 @@
         <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2552</v>
+        <v>4478</v>
       </c>
       <c r="C2" t="n">
-        <v>11295</v>
+        <v>6295</v>
       </c>
       <c r="D2" t="n">
-        <v>16828</v>
+        <v>19441</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2792</v>
+        <v>4196</v>
       </c>
       <c r="C3" t="n">
-        <v>6893</v>
+        <v>7577</v>
       </c>
       <c r="D3" t="n">
-        <v>15719</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2261</v>
+        <v>3236</v>
       </c>
       <c r="C4" t="n">
-        <v>10952</v>
+        <v>10586</v>
       </c>
       <c r="D4" t="n">
-        <v>10885</v>
+        <v>10061</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1315</v>
+        <v>1800</v>
       </c>
       <c r="C5" t="n">
-        <v>9003</v>
+        <v>7920</v>
       </c>
       <c r="D5" t="n">
-        <v>4443</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>818</v>
+        <v>1096</v>
       </c>
       <c r="C6" t="n">
-        <v>5240</v>
+        <v>4655</v>
       </c>
       <c r="D6" t="n">
-        <v>1328</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>386</v>
+        <v>507</v>
       </c>
       <c r="C7" t="n">
-        <v>3028</v>
+        <v>3061</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="C8" t="n">
-        <v>1613</v>
+        <v>1880</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>677</v>
+        <v>829</v>
       </c>
       <c r="D9" t="n">
         <v>261</v>
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2537,7 +2537,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1545</v>
+        <v>2729</v>
       </c>
       <c r="C2" t="n">
-        <v>5438</v>
+        <v>3093</v>
       </c>
       <c r="D2" t="n">
-        <v>11728</v>
+        <v>13594</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2644</v>
+        <v>4113</v>
       </c>
       <c r="C3" t="n">
-        <v>8114</v>
+        <v>6960</v>
       </c>
       <c r="D3" t="n">
-        <v>15482</v>
+        <v>15300</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2479</v>
+        <v>3551</v>
       </c>
       <c r="C4" t="n">
-        <v>10528</v>
+        <v>10457</v>
       </c>
       <c r="D4" t="n">
-        <v>11579</v>
+        <v>10755</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1386</v>
+        <v>1884</v>
       </c>
       <c r="C5" t="n">
-        <v>10845</v>
+        <v>9772</v>
       </c>
       <c r="D5" t="n">
-        <v>4649</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>674</v>
+        <v>893</v>
       </c>
       <c r="C6" t="n">
-        <v>6043</v>
+        <v>5444</v>
       </c>
       <c r="D6" t="n">
-        <v>1283</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
-        <v>3080</v>
+        <v>3287</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1121</v>
+        <v>1346</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
         <v>284</v>
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2806,7 +2806,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2834,7 +2834,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2620</v>
+        <v>4109</v>
       </c>
       <c r="C2" t="n">
-        <v>8746</v>
+        <v>2858</v>
       </c>
       <c r="D2" t="n">
-        <v>10170</v>
+        <v>13058</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1901</v>
+        <v>3059</v>
       </c>
       <c r="C3" t="n">
-        <v>6216</v>
+        <v>4728</v>
       </c>
       <c r="D3" t="n">
-        <v>13985</v>
+        <v>14077</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2227</v>
+        <v>3293</v>
       </c>
       <c r="C4" t="n">
-        <v>9320</v>
+        <v>8661</v>
       </c>
       <c r="D4" t="n">
-        <v>11826</v>
+        <v>11126</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1614</v>
+        <v>2247</v>
       </c>
       <c r="C5" t="n">
-        <v>10485</v>
+        <v>9958</v>
       </c>
       <c r="D5" t="n">
-        <v>5550</v>
+        <v>4882</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>1141</v>
       </c>
       <c r="C6" t="n">
-        <v>8044</v>
+        <v>7194</v>
       </c>
       <c r="D6" t="n">
-        <v>1686</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>4212</v>
+        <v>4174</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1814</v>
+        <v>2037</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>544</v>
+        <v>635</v>
       </c>
       <c r="D9" t="n">
         <v>291</v>
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3173,7 +3173,7 @@
         <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1627</v>
+        <v>2924</v>
       </c>
       <c r="C2" t="n">
-        <v>4732</v>
+        <v>2019</v>
       </c>
       <c r="D2" t="n">
-        <v>7861</v>
+        <v>9483</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1857</v>
+        <v>2961</v>
       </c>
       <c r="C3" t="n">
-        <v>6519</v>
+        <v>3683</v>
       </c>
       <c r="D3" t="n">
-        <v>12819</v>
+        <v>13219</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1971</v>
+        <v>2946</v>
       </c>
       <c r="C4" t="n">
-        <v>8202</v>
+        <v>7220</v>
       </c>
       <c r="D4" t="n">
-        <v>11849</v>
+        <v>11262</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1706</v>
+        <v>2437</v>
       </c>
       <c r="C5" t="n">
-        <v>10278</v>
+        <v>9601</v>
       </c>
       <c r="D5" t="n">
-        <v>6150</v>
+        <v>5486</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>973</v>
+        <v>1312</v>
       </c>
       <c r="C6" t="n">
-        <v>9067</v>
+        <v>8296</v>
       </c>
       <c r="D6" t="n">
-        <v>1995</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>5284</v>
+        <v>5139</v>
       </c>
       <c r="D7" t="n">
-        <v>726</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>2357</v>
+        <v>2546</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>581</v>
+        <v>697</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3470,7 +3470,7 @@
         <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1757</v>
+        <v>3636</v>
       </c>
       <c r="C2" t="n">
-        <v>13043</v>
+        <v>10884</v>
       </c>
       <c r="D2" t="n">
-        <v>14492</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1502</v>
+        <v>2483</v>
       </c>
       <c r="C3" t="n">
-        <v>5282</v>
+        <v>2729</v>
       </c>
       <c r="D3" t="n">
-        <v>11463</v>
+        <v>11975</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1680</v>
+        <v>2564</v>
       </c>
       <c r="C4" t="n">
-        <v>7368</v>
+        <v>5643</v>
       </c>
       <c r="D4" t="n">
-        <v>11619</v>
+        <v>11182</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1639</v>
+        <v>2401</v>
       </c>
       <c r="C5" t="n">
-        <v>9188</v>
+        <v>8486</v>
       </c>
       <c r="D5" t="n">
-        <v>6674</v>
+        <v>5987</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1122</v>
+        <v>1537</v>
       </c>
       <c r="C6" t="n">
-        <v>9436</v>
+        <v>8705</v>
       </c>
       <c r="D6" t="n">
-        <v>2428</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>390</v>
+        <v>529</v>
       </c>
       <c r="C7" t="n">
-        <v>6668</v>
+        <v>6250</v>
       </c>
       <c r="D7" t="n">
-        <v>867</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>3302</v>
+        <v>3433</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1126</v>
+        <v>1258</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4365</v>
+        <v>7457</v>
       </c>
       <c r="C2" t="n">
-        <v>8013</v>
+        <v>12231</v>
       </c>
       <c r="D2" t="n">
-        <v>2602</v>
+        <v>5384</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>2659</v>
       </c>
       <c r="C2" t="n">
-        <v>7825</v>
+        <v>6443</v>
       </c>
       <c r="D2" t="n">
-        <v>10782</v>
+        <v>8107</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1964</v>
+        <v>3229</v>
       </c>
       <c r="C3" t="n">
-        <v>7465</v>
+        <v>4728</v>
       </c>
       <c r="D3" t="n">
-        <v>12708</v>
+        <v>12964</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2373</v>
+        <v>3528</v>
       </c>
       <c r="C4" t="n">
-        <v>10373</v>
+        <v>8423</v>
       </c>
       <c r="D4" t="n">
-        <v>11927</v>
+        <v>11312</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1036</v>
+        <v>1442</v>
       </c>
       <c r="C5" t="n">
-        <v>13408</v>
+        <v>12290</v>
       </c>
       <c r="D5" t="n">
-        <v>5954</v>
+        <v>5428</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>360</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
-        <v>8106</v>
+        <v>7660</v>
       </c>
       <c r="D6" t="n">
-        <v>1913</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>3235</v>
+        <v>3364</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1103</v>
+        <v>1232</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6526</v>
+        <v>7310</v>
       </c>
       <c r="C2" t="n">
-        <v>5712</v>
+        <v>9660</v>
       </c>
       <c r="D2" t="n">
-        <v>20683</v>
+        <v>15962</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1856</v>
+        <v>3167</v>
       </c>
       <c r="C3" t="n">
-        <v>4102</v>
+        <v>6164</v>
       </c>
       <c r="D3" t="n">
-        <v>1097</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4287</v>
+        <v>6369</v>
       </c>
       <c r="C2" t="n">
-        <v>6221</v>
+        <v>4030</v>
       </c>
       <c r="D2" t="n">
-        <v>30508</v>
+        <v>18377</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3437</v>
+        <v>4304</v>
       </c>
       <c r="C3" t="n">
-        <v>4323</v>
+        <v>7021</v>
       </c>
       <c r="D3" t="n">
-        <v>4306</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>840</v>
+        <v>1410</v>
       </c>
       <c r="C4" t="n">
-        <v>2445</v>
+        <v>3655</v>
       </c>
       <c r="D4" t="n">
-        <v>1402</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4611</v>
+        <v>6133</v>
       </c>
       <c r="C2" t="n">
-        <v>11027</v>
+        <v>10489</v>
       </c>
       <c r="D2" t="n">
-        <v>31852</v>
+        <v>18840</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3173</v>
+        <v>4403</v>
       </c>
       <c r="C3" t="n">
-        <v>4637</v>
+        <v>4700</v>
       </c>
       <c r="D3" t="n">
-        <v>8188</v>
+        <v>5897</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1814</v>
+        <v>2396</v>
       </c>
       <c r="C4" t="n">
-        <v>3457</v>
+        <v>5453</v>
       </c>
       <c r="D4" t="n">
-        <v>1916</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>398</v>
+        <v>628</v>
       </c>
       <c r="C5" t="n">
-        <v>1432</v>
+        <v>2061</v>
       </c>
       <c r="D5" t="n">
-        <v>1177</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4652</v>
+        <v>6003</v>
       </c>
       <c r="C2" t="n">
-        <v>10015</v>
+        <v>6023</v>
       </c>
       <c r="D2" t="n">
-        <v>24973</v>
+        <v>28194</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3193</v>
+        <v>4282</v>
       </c>
       <c r="C3" t="n">
-        <v>6898</v>
+        <v>6645</v>
       </c>
       <c r="D3" t="n">
-        <v>11208</v>
+        <v>7449</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2093</v>
+        <v>2868</v>
       </c>
       <c r="C4" t="n">
-        <v>4019</v>
+        <v>4941</v>
       </c>
       <c r="D4" t="n">
-        <v>3001</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>901</v>
+        <v>1228</v>
       </c>
       <c r="C5" t="n">
-        <v>2451</v>
+        <v>3724</v>
       </c>
       <c r="D5" t="n">
-        <v>1257</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>859</v>
+        <v>1177</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4538</v>
+        <v>6830</v>
       </c>
       <c r="C2" t="n">
-        <v>9658</v>
+        <v>5939</v>
       </c>
       <c r="D2" t="n">
-        <v>30679</v>
+        <v>30267</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2838</v>
+        <v>3707</v>
       </c>
       <c r="C3" t="n">
-        <v>6955</v>
+        <v>5192</v>
       </c>
       <c r="D3" t="n">
-        <v>11771</v>
+        <v>9546</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1641</v>
+        <v>2191</v>
       </c>
       <c r="C4" t="n">
-        <v>4592</v>
+        <v>4797</v>
       </c>
       <c r="D4" t="n">
-        <v>3848</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>771</v>
+        <v>1062</v>
       </c>
       <c r="C5" t="n">
-        <v>2383</v>
+        <v>3163</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>268</v>
+        <v>360</v>
       </c>
       <c r="C6" t="n">
-        <v>1102</v>
+        <v>1614</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>752</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>384</v>
+        <v>478</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4113</v>
+        <v>5468</v>
       </c>
       <c r="C2" t="n">
-        <v>8202</v>
+        <v>5799</v>
       </c>
       <c r="D2" t="n">
-        <v>24912</v>
+        <v>26121</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3048</v>
+        <v>4357</v>
       </c>
       <c r="C3" t="n">
-        <v>7338</v>
+        <v>4839</v>
       </c>
       <c r="D3" t="n">
-        <v>14081</v>
+        <v>12324</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1942</v>
+        <v>2575</v>
       </c>
       <c r="C4" t="n">
-        <v>5925</v>
+        <v>4932</v>
       </c>
       <c r="D4" t="n">
-        <v>5291</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1076</v>
+        <v>1443</v>
       </c>
       <c r="C5" t="n">
-        <v>3627</v>
+        <v>4038</v>
       </c>
       <c r="D5" t="n">
-        <v>1713</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>480</v>
+        <v>647</v>
       </c>
       <c r="C6" t="n">
-        <v>1814</v>
+        <v>2457</v>
       </c>
       <c r="D6" t="n">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="C7" t="n">
-        <v>784</v>
+        <v>1096</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>309</v>
+        <v>359</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4107</v>
+        <v>4862</v>
       </c>
       <c r="C2" t="n">
-        <v>11501</v>
+        <v>13434</v>
       </c>
       <c r="D2" t="n">
-        <v>21813</v>
+        <v>26060</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2929</v>
+        <v>4030</v>
       </c>
       <c r="C3" t="n">
-        <v>6764</v>
+        <v>4641</v>
       </c>
       <c r="D3" t="n">
-        <v>14800</v>
+        <v>13553</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2123</v>
+        <v>2966</v>
       </c>
       <c r="C4" t="n">
-        <v>6588</v>
+        <v>4731</v>
       </c>
       <c r="D4" t="n">
-        <v>6817</v>
+        <v>5466</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1324</v>
+        <v>1742</v>
       </c>
       <c r="C5" t="n">
-        <v>4752</v>
+        <v>4434</v>
       </c>
       <c r="D5" t="n">
-        <v>2313</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>695</v>
+        <v>940</v>
       </c>
       <c r="C6" t="n">
-        <v>2750</v>
+        <v>3249</v>
       </c>
       <c r="D6" t="n">
-        <v>967</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>368</v>
       </c>
       <c r="C7" t="n">
-        <v>1318</v>
+        <v>1789</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>546</v>
+        <v>716</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_17_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6371</v>
+        <v>4830</v>
       </c>
       <c r="C2" t="n">
-        <v>14534</v>
+        <v>7865</v>
       </c>
       <c r="D2" t="n">
-        <v>30227</v>
+        <v>51132</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3634</v>
+        <v>3072</v>
       </c>
       <c r="C3" t="n">
-        <v>7790</v>
+        <v>6312</v>
       </c>
       <c r="D3" t="n">
-        <v>14421</v>
+        <v>22530</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2976</v>
+        <v>2663</v>
       </c>
       <c r="C4" t="n">
-        <v>4586</v>
+        <v>5715</v>
       </c>
       <c r="D4" t="n">
-        <v>6697</v>
+        <v>10492</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2011</v>
+        <v>1847</v>
       </c>
       <c r="C5" t="n">
-        <v>4487</v>
+        <v>3635</v>
       </c>
       <c r="D5" t="n">
-        <v>2409</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1181</v>
+        <v>1021</v>
       </c>
       <c r="C6" t="n">
-        <v>3741</v>
+        <v>2772</v>
       </c>
       <c r="D6" t="n">
-        <v>1062</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>558</v>
+        <v>447</v>
       </c>
       <c r="C7" t="n">
-        <v>2475</v>
+        <v>1777</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C8" t="n">
-        <v>1192</v>
+        <v>891</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>472</v>
+        <v>385</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7722</v>
+        <v>5264</v>
       </c>
       <c r="C2" t="n">
-        <v>9520</v>
+        <v>12320</v>
       </c>
       <c r="D2" t="n">
-        <v>23877</v>
+        <v>51265</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3896</v>
+        <v>3116</v>
       </c>
       <c r="C3" t="n">
-        <v>9469</v>
+        <v>6171</v>
       </c>
       <c r="D3" t="n">
-        <v>15498</v>
+        <v>24713</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2785</v>
+        <v>2430</v>
       </c>
       <c r="C4" t="n">
-        <v>5967</v>
+        <v>5816</v>
       </c>
       <c r="D4" t="n">
-        <v>7615</v>
+        <v>11921</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2159</v>
+        <v>1942</v>
       </c>
       <c r="C5" t="n">
-        <v>4394</v>
+        <v>4497</v>
       </c>
       <c r="D5" t="n">
-        <v>2994</v>
+        <v>4526</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1385</v>
+        <v>1252</v>
       </c>
       <c r="C6" t="n">
-        <v>3991</v>
+        <v>3091</v>
       </c>
       <c r="D6" t="n">
-        <v>1231</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>727</v>
+        <v>608</v>
       </c>
       <c r="C7" t="n">
-        <v>3019</v>
+        <v>2205</v>
       </c>
       <c r="D7" t="n">
-        <v>692</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>301</v>
+        <v>242</v>
       </c>
       <c r="C8" t="n">
-        <v>1707</v>
+        <v>1246</v>
       </c>
       <c r="D8" t="n">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>761</v>
+        <v>588</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>277</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8247</v>
+        <v>7089</v>
       </c>
       <c r="C2" t="n">
-        <v>15926</v>
+        <v>7364</v>
       </c>
       <c r="D2" t="n">
-        <v>25985</v>
+        <v>51243</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4348</v>
+        <v>3215</v>
       </c>
       <c r="C3" t="n">
-        <v>8456</v>
+        <v>7654</v>
       </c>
       <c r="D3" t="n">
-        <v>15511</v>
+        <v>26317</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2737</v>
+        <v>2301</v>
       </c>
       <c r="C4" t="n">
-        <v>7231</v>
+        <v>5844</v>
       </c>
       <c r="D4" t="n">
-        <v>8518</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2147</v>
+        <v>1908</v>
       </c>
       <c r="C5" t="n">
-        <v>4894</v>
+        <v>4892</v>
       </c>
       <c r="D5" t="n">
-        <v>3495</v>
+        <v>5338</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1535</v>
+        <v>1385</v>
       </c>
       <c r="C6" t="n">
-        <v>4115</v>
+        <v>3587</v>
       </c>
       <c r="D6" t="n">
-        <v>1451</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>879</v>
+        <v>763</v>
       </c>
       <c r="C7" t="n">
-        <v>3359</v>
+        <v>2551</v>
       </c>
       <c r="D7" t="n">
-        <v>746</v>
+        <v>837</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>409</v>
+        <v>334</v>
       </c>
       <c r="C8" t="n">
-        <v>2178</v>
+        <v>1590</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="C9" t="n">
-        <v>1096</v>
+        <v>820</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>472</v>
+        <v>386</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7606</v>
+        <v>6417</v>
       </c>
       <c r="C2" t="n">
-        <v>11084</v>
+        <v>5125</v>
       </c>
       <c r="D2" t="n">
-        <v>21532</v>
+        <v>42257</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5036</v>
+        <v>3960</v>
       </c>
       <c r="C3" t="n">
-        <v>12897</v>
+        <v>10582</v>
       </c>
       <c r="D3" t="n">
-        <v>16762</v>
+        <v>28117</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1983</v>
+        <v>1762</v>
       </c>
       <c r="C4" t="n">
-        <v>8516</v>
+        <v>7838</v>
       </c>
       <c r="D4" t="n">
-        <v>7976</v>
+        <v>12437</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1418</v>
+        <v>1279</v>
       </c>
       <c r="C5" t="n">
-        <v>4032</v>
+        <v>3515</v>
       </c>
       <c r="D5" t="n">
-        <v>2361</v>
+        <v>3361</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>812</v>
+        <v>705</v>
       </c>
       <c r="C6" t="n">
-        <v>3291</v>
+        <v>2499</v>
       </c>
       <c r="D6" t="n">
-        <v>731</v>
+        <v>820</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>2134</v>
+        <v>1558</v>
       </c>
       <c r="D7" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>1074</v>
+        <v>803</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>462</v>
+        <v>378</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4617</v>
+        <v>4022</v>
       </c>
       <c r="C2" t="n">
-        <v>5487</v>
+        <v>2786</v>
       </c>
       <c r="D2" t="n">
-        <v>15490</v>
+        <v>28959</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5247</v>
+        <v>4262</v>
       </c>
       <c r="C3" t="n">
-        <v>10995</v>
+        <v>7434</v>
       </c>
       <c r="D3" t="n">
-        <v>16433</v>
+        <v>28352</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2699</v>
+        <v>2254</v>
       </c>
       <c r="C4" t="n">
-        <v>10642</v>
+        <v>9214</v>
       </c>
       <c r="D4" t="n">
-        <v>9151</v>
+        <v>14555</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1558</v>
+        <v>1400</v>
       </c>
       <c r="C5" t="n">
-        <v>5906</v>
+        <v>5312</v>
       </c>
       <c r="D5" t="n">
-        <v>2981</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>952</v>
+        <v>830</v>
       </c>
       <c r="C6" t="n">
-        <v>3702</v>
+        <v>2959</v>
       </c>
       <c r="D6" t="n">
-        <v>884</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>348</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>2616</v>
+        <v>1934</v>
       </c>
       <c r="D7" t="n">
-        <v>498</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>1385</v>
+        <v>1033</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>498</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
         <v>256</v>
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
         <v>208</v>
@@ -2156,7 +2156,7 @@
         <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4478</v>
+        <v>3728</v>
       </c>
       <c r="C2" t="n">
-        <v>6295</v>
+        <v>5239</v>
       </c>
       <c r="D2" t="n">
-        <v>19441</v>
+        <v>29653</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4196</v>
+        <v>3497</v>
       </c>
       <c r="C3" t="n">
-        <v>7577</v>
+        <v>4754</v>
       </c>
       <c r="D3" t="n">
-        <v>15200</v>
+        <v>26529</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3236</v>
+        <v>2662</v>
       </c>
       <c r="C4" t="n">
-        <v>10586</v>
+        <v>8185</v>
       </c>
       <c r="D4" t="n">
-        <v>10061</v>
+        <v>16364</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1800</v>
+        <v>1564</v>
       </c>
       <c r="C5" t="n">
-        <v>7920</v>
+        <v>6962</v>
       </c>
       <c r="D5" t="n">
-        <v>3838</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1096</v>
+        <v>968</v>
       </c>
       <c r="C6" t="n">
-        <v>4655</v>
+        <v>3976</v>
       </c>
       <c r="D6" t="n">
-        <v>1174</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>507</v>
+        <v>429</v>
       </c>
       <c r="C7" t="n">
-        <v>3061</v>
+        <v>2355</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>1880</v>
+        <v>1395</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>829</v>
+        <v>645</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2509,7 +2509,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2729</v>
+        <v>2265</v>
       </c>
       <c r="C2" t="n">
-        <v>3093</v>
+        <v>2536</v>
       </c>
       <c r="D2" t="n">
-        <v>13594</v>
+        <v>20680</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4113</v>
+        <v>3427</v>
       </c>
       <c r="C3" t="n">
-        <v>6960</v>
+        <v>4779</v>
       </c>
       <c r="D3" t="n">
-        <v>15300</v>
+        <v>26259</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3551</v>
+        <v>2943</v>
       </c>
       <c r="C4" t="n">
-        <v>10457</v>
+        <v>7746</v>
       </c>
       <c r="D4" t="n">
-        <v>10755</v>
+        <v>17585</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1884</v>
+        <v>1637</v>
       </c>
       <c r="C5" t="n">
-        <v>9772</v>
+        <v>8260</v>
       </c>
       <c r="D5" t="n">
-        <v>4038</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>893</v>
+        <v>781</v>
       </c>
       <c r="C6" t="n">
-        <v>5444</v>
+        <v>4675</v>
       </c>
       <c r="D6" t="n">
-        <v>1145</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>3287</v>
+        <v>2480</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>1346</v>
+        <v>1042</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>313</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
         <v>284</v>
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2806,7 +2806,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4109</v>
+        <v>2799</v>
       </c>
       <c r="C2" t="n">
-        <v>2858</v>
+        <v>7690</v>
       </c>
       <c r="D2" t="n">
-        <v>13058</v>
+        <v>16077</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3059</v>
+        <v>2546</v>
       </c>
       <c r="C3" t="n">
-        <v>4728</v>
+        <v>3405</v>
       </c>
       <c r="D3" t="n">
-        <v>14077</v>
+        <v>23822</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3293</v>
+        <v>2735</v>
       </c>
       <c r="C4" t="n">
-        <v>8661</v>
+        <v>6246</v>
       </c>
       <c r="D4" t="n">
-        <v>11126</v>
+        <v>18382</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2247</v>
+        <v>1911</v>
       </c>
       <c r="C5" t="n">
-        <v>9958</v>
+        <v>7945</v>
       </c>
       <c r="D5" t="n">
-        <v>4882</v>
+        <v>7606</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1141</v>
+        <v>995</v>
       </c>
       <c r="C6" t="n">
-        <v>7194</v>
+        <v>6125</v>
       </c>
       <c r="D6" t="n">
-        <v>1530</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>275</v>
       </c>
       <c r="C7" t="n">
-        <v>4174</v>
+        <v>3366</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2037</v>
+        <v>1555</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>635</v>
+        <v>518</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3117,7 +3117,7 @@
         <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2924</v>
+        <v>1920</v>
       </c>
       <c r="C2" t="n">
-        <v>2019</v>
+        <v>4055</v>
       </c>
       <c r="D2" t="n">
-        <v>9483</v>
+        <v>11814</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2961</v>
+        <v>2301</v>
       </c>
       <c r="C3" t="n">
-        <v>3683</v>
+        <v>4606</v>
       </c>
       <c r="D3" t="n">
-        <v>13219</v>
+        <v>21696</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2946</v>
+        <v>2469</v>
       </c>
       <c r="C4" t="n">
-        <v>7220</v>
+        <v>5145</v>
       </c>
       <c r="D4" t="n">
-        <v>11262</v>
+        <v>18678</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2437</v>
+        <v>2060</v>
       </c>
       <c r="C5" t="n">
-        <v>9601</v>
+        <v>7497</v>
       </c>
       <c r="D5" t="n">
-        <v>5486</v>
+        <v>8658</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1312</v>
+        <v>1136</v>
       </c>
       <c r="C6" t="n">
-        <v>8296</v>
+        <v>6910</v>
       </c>
       <c r="D6" t="n">
-        <v>1799</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>5139</v>
+        <v>4217</v>
       </c>
       <c r="D7" t="n">
-        <v>683</v>
+        <v>771</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>2546</v>
+        <v>1970</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>697</v>
+        <v>570</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3414,7 +3414,7 @@
         <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3636</v>
+        <v>2530</v>
       </c>
       <c r="C2" t="n">
-        <v>10884</v>
+        <v>5371</v>
       </c>
       <c r="D2" t="n">
-        <v>10896</v>
+        <v>15554</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2483</v>
+        <v>1831</v>
       </c>
       <c r="C3" t="n">
-        <v>2729</v>
+        <v>3959</v>
       </c>
       <c r="D3" t="n">
-        <v>11975</v>
+        <v>19329</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2564</v>
+        <v>2096</v>
       </c>
       <c r="C4" t="n">
-        <v>5643</v>
+        <v>4820</v>
       </c>
       <c r="D4" t="n">
-        <v>11182</v>
+        <v>18336</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2401</v>
+        <v>2005</v>
       </c>
       <c r="C5" t="n">
-        <v>8486</v>
+        <v>6437</v>
       </c>
       <c r="D5" t="n">
-        <v>5987</v>
+        <v>9741</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1537</v>
+        <v>1337</v>
       </c>
       <c r="C6" t="n">
-        <v>8705</v>
+        <v>7068</v>
       </c>
       <c r="D6" t="n">
-        <v>2236</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>529</v>
+        <v>456</v>
       </c>
       <c r="C7" t="n">
-        <v>6250</v>
+        <v>5165</v>
       </c>
       <c r="D7" t="n">
-        <v>807</v>
+        <v>969</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>3433</v>
+        <v>2717</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1258</v>
+        <v>1014</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3725,7 +3725,7 @@
         <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7457</v>
+        <v>4756</v>
       </c>
       <c r="C2" t="n">
-        <v>12231</v>
+        <v>8338</v>
       </c>
       <c r="D2" t="n">
-        <v>5384</v>
+        <v>8102</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2659</v>
+        <v>1849</v>
       </c>
       <c r="C2" t="n">
-        <v>6443</v>
+        <v>3137</v>
       </c>
       <c r="D2" t="n">
-        <v>8107</v>
+        <v>11573</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3229</v>
+        <v>2438</v>
       </c>
       <c r="C3" t="n">
-        <v>4728</v>
+        <v>4618</v>
       </c>
       <c r="D3" t="n">
-        <v>12964</v>
+        <v>20835</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3528</v>
+        <v>2923</v>
       </c>
       <c r="C4" t="n">
-        <v>8423</v>
+        <v>7070</v>
       </c>
       <c r="D4" t="n">
-        <v>11312</v>
+        <v>18532</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1442</v>
+        <v>1253</v>
       </c>
       <c r="C5" t="n">
-        <v>12290</v>
+        <v>9758</v>
       </c>
       <c r="D5" t="n">
-        <v>5428</v>
+        <v>8642</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>488</v>
+        <v>421</v>
       </c>
       <c r="C6" t="n">
-        <v>7660</v>
+        <v>6308</v>
       </c>
       <c r="D6" t="n">
-        <v>1769</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>3364</v>
+        <v>2662</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1232</v>
+        <v>993</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4333,7 +4333,7 @@
         <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7310</v>
+        <v>6217</v>
       </c>
       <c r="C2" t="n">
-        <v>9660</v>
+        <v>5532</v>
       </c>
       <c r="D2" t="n">
-        <v>15962</v>
+        <v>24611</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3167</v>
+        <v>2022</v>
       </c>
       <c r="C3" t="n">
-        <v>6164</v>
+        <v>4202</v>
       </c>
       <c r="D3" t="n">
-        <v>1543</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6369</v>
+        <v>5557</v>
       </c>
       <c r="C2" t="n">
-        <v>4030</v>
+        <v>5976</v>
       </c>
       <c r="D2" t="n">
-        <v>18377</v>
+        <v>31026</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4304</v>
+        <v>3380</v>
       </c>
       <c r="C3" t="n">
-        <v>7021</v>
+        <v>4272</v>
       </c>
       <c r="D3" t="n">
-        <v>3851</v>
+        <v>5651</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1410</v>
+        <v>912</v>
       </c>
       <c r="C4" t="n">
-        <v>3655</v>
+        <v>2505</v>
       </c>
       <c r="D4" t="n">
-        <v>1492</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6133</v>
+        <v>6497</v>
       </c>
       <c r="C2" t="n">
-        <v>10489</v>
+        <v>5934</v>
       </c>
       <c r="D2" t="n">
-        <v>18840</v>
+        <v>40294</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4403</v>
+        <v>3647</v>
       </c>
       <c r="C3" t="n">
-        <v>4700</v>
+        <v>4543</v>
       </c>
       <c r="D3" t="n">
-        <v>5897</v>
+        <v>9304</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2396</v>
+        <v>1822</v>
       </c>
       <c r="C4" t="n">
-        <v>5453</v>
+        <v>3412</v>
       </c>
       <c r="D4" t="n">
-        <v>1899</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>628</v>
+        <v>427</v>
       </c>
       <c r="C5" t="n">
-        <v>2061</v>
+        <v>1465</v>
       </c>
       <c r="D5" t="n">
-        <v>1203</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
         <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6003</v>
+        <v>5989</v>
       </c>
       <c r="C2" t="n">
-        <v>6023</v>
+        <v>5188</v>
       </c>
       <c r="D2" t="n">
-        <v>28194</v>
+        <v>42185</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4282</v>
+        <v>4068</v>
       </c>
       <c r="C3" t="n">
-        <v>6645</v>
+        <v>4573</v>
       </c>
       <c r="D3" t="n">
-        <v>7449</v>
+        <v>13359</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2868</v>
+        <v>2283</v>
       </c>
       <c r="C4" t="n">
-        <v>4941</v>
+        <v>3905</v>
       </c>
       <c r="D4" t="n">
-        <v>2570</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1228</v>
+        <v>923</v>
       </c>
       <c r="C5" t="n">
-        <v>3724</v>
+        <v>2443</v>
       </c>
       <c r="D5" t="n">
-        <v>1275</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>248</v>
       </c>
       <c r="C6" t="n">
-        <v>1177</v>
+        <v>880</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5557,7 +5557,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
         <v>233</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6830</v>
+        <v>5807</v>
       </c>
       <c r="C2" t="n">
-        <v>5939</v>
+        <v>6794</v>
       </c>
       <c r="D2" t="n">
-        <v>30267</v>
+        <v>39275</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3707</v>
+        <v>3619</v>
       </c>
       <c r="C3" t="n">
-        <v>5192</v>
+        <v>4001</v>
       </c>
       <c r="D3" t="n">
-        <v>9546</v>
+        <v>15805</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2191</v>
+        <v>1939</v>
       </c>
       <c r="C4" t="n">
-        <v>4797</v>
+        <v>3461</v>
       </c>
       <c r="D4" t="n">
-        <v>2884</v>
+        <v>4548</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1062</v>
+        <v>822</v>
       </c>
       <c r="C5" t="n">
-        <v>3163</v>
+        <v>2336</v>
       </c>
       <c r="D5" t="n">
-        <v>1182</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>1614</v>
+        <v>1112</v>
       </c>
       <c r="D6" t="n">
-        <v>752</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>478</v>
+        <v>384</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5468</v>
+        <v>4864</v>
       </c>
       <c r="C2" t="n">
-        <v>5799</v>
+        <v>11526</v>
       </c>
       <c r="D2" t="n">
-        <v>26121</v>
+        <v>44039</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4357</v>
+        <v>3895</v>
       </c>
       <c r="C3" t="n">
-        <v>4839</v>
+        <v>4829</v>
       </c>
       <c r="D3" t="n">
-        <v>12324</v>
+        <v>18584</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2575</v>
+        <v>2429</v>
       </c>
       <c r="C4" t="n">
-        <v>4932</v>
+        <v>3710</v>
       </c>
       <c r="D4" t="n">
-        <v>4139</v>
+        <v>6679</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1443</v>
+        <v>1213</v>
       </c>
       <c r="C5" t="n">
-        <v>4038</v>
+        <v>2912</v>
       </c>
       <c r="D5" t="n">
-        <v>1461</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>647</v>
+        <v>507</v>
       </c>
       <c r="C6" t="n">
-        <v>2457</v>
+        <v>1791</v>
       </c>
       <c r="D6" t="n">
-        <v>823</v>
+        <v>874</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>1096</v>
+        <v>790</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>359</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4862</v>
+        <v>3859</v>
       </c>
       <c r="C2" t="n">
-        <v>13434</v>
+        <v>7077</v>
       </c>
       <c r="D2" t="n">
-        <v>26060</v>
+        <v>40877</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4030</v>
+        <v>3593</v>
       </c>
       <c r="C3" t="n">
-        <v>4641</v>
+        <v>7341</v>
       </c>
       <c r="D3" t="n">
-        <v>13553</v>
+        <v>21144</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2966</v>
+        <v>2710</v>
       </c>
       <c r="C4" t="n">
-        <v>4731</v>
+        <v>4209</v>
       </c>
       <c r="D4" t="n">
-        <v>5466</v>
+        <v>8583</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1742</v>
+        <v>1568</v>
       </c>
       <c r="C5" t="n">
-        <v>4434</v>
+        <v>3280</v>
       </c>
       <c r="D5" t="n">
-        <v>1905</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>940</v>
+        <v>771</v>
       </c>
       <c r="C6" t="n">
-        <v>3249</v>
+        <v>2352</v>
       </c>
       <c r="D6" t="n">
-        <v>913</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>368</v>
+        <v>288</v>
       </c>
       <c r="C7" t="n">
-        <v>1789</v>
+        <v>1292</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>716</v>
+        <v>549</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">

--- a/output/yearly_population_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_17_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4830</v>
+        <v>904</v>
       </c>
       <c r="C2" t="n">
-        <v>7865</v>
+        <v>3687</v>
       </c>
       <c r="D2" t="n">
-        <v>51132</v>
+        <v>12447</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3072</v>
+        <v>1588</v>
       </c>
       <c r="C3" t="n">
-        <v>6312</v>
+        <v>8803</v>
       </c>
       <c r="D3" t="n">
-        <v>22530</v>
+        <v>14115</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2663</v>
+        <v>1153</v>
       </c>
       <c r="C4" t="n">
-        <v>5715</v>
+        <v>10609</v>
       </c>
       <c r="D4" t="n">
-        <v>10492</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1847</v>
+        <v>613</v>
       </c>
       <c r="C5" t="n">
-        <v>3635</v>
+        <v>6553</v>
       </c>
       <c r="D5" t="n">
-        <v>3572</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1021</v>
+        <v>269</v>
       </c>
       <c r="C6" t="n">
-        <v>2772</v>
+        <v>2491</v>
       </c>
       <c r="D6" t="n">
-        <v>1295</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>447</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>1777</v>
+        <v>861</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>891</v>
+        <v>360</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5264</v>
+        <v>1013</v>
       </c>
       <c r="C2" t="n">
-        <v>12320</v>
+        <v>8427</v>
       </c>
       <c r="D2" t="n">
-        <v>51265</v>
+        <v>16058</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3116</v>
+        <v>1090</v>
       </c>
       <c r="C3" t="n">
-        <v>6171</v>
+        <v>5425</v>
       </c>
       <c r="D3" t="n">
-        <v>24713</v>
+        <v>13003</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2430</v>
+        <v>1165</v>
       </c>
       <c r="C4" t="n">
-        <v>5816</v>
+        <v>9536</v>
       </c>
       <c r="D4" t="n">
-        <v>11921</v>
+        <v>7556</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1942</v>
+        <v>763</v>
       </c>
       <c r="C5" t="n">
-        <v>4497</v>
+        <v>8441</v>
       </c>
       <c r="D5" t="n">
-        <v>4526</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1252</v>
+        <v>376</v>
       </c>
       <c r="C6" t="n">
-        <v>3091</v>
+        <v>4439</v>
       </c>
       <c r="D6" t="n">
-        <v>1593</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>608</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>2205</v>
+        <v>1619</v>
       </c>
       <c r="D7" t="n">
-        <v>744</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>242</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1246</v>
+        <v>579</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>588</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7089</v>
+        <v>556</v>
       </c>
       <c r="C2" t="n">
-        <v>7364</v>
+        <v>3666</v>
       </c>
       <c r="D2" t="n">
-        <v>51243</v>
+        <v>10980</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3215</v>
+        <v>1030</v>
       </c>
       <c r="C3" t="n">
-        <v>7654</v>
+        <v>6330</v>
       </c>
       <c r="D3" t="n">
-        <v>26317</v>
+        <v>13036</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2301</v>
+        <v>1270</v>
       </c>
       <c r="C4" t="n">
-        <v>5844</v>
+        <v>8844</v>
       </c>
       <c r="D4" t="n">
-        <v>13400</v>
+        <v>8336</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1908</v>
+        <v>769</v>
       </c>
       <c r="C5" t="n">
-        <v>4892</v>
+        <v>9749</v>
       </c>
       <c r="D5" t="n">
-        <v>5338</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1385</v>
+        <v>301</v>
       </c>
       <c r="C6" t="n">
-        <v>3587</v>
+        <v>5468</v>
       </c>
       <c r="D6" t="n">
-        <v>1966</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>763</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2551</v>
+        <v>1485</v>
       </c>
       <c r="D7" t="n">
-        <v>837</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>334</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1590</v>
+        <v>501</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>820</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>386</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>211</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6417</v>
+        <v>420</v>
       </c>
       <c r="C2" t="n">
-        <v>5125</v>
+        <v>7389</v>
       </c>
       <c r="D2" t="n">
-        <v>42257</v>
+        <v>13090</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3960</v>
+        <v>700</v>
       </c>
       <c r="C3" t="n">
-        <v>10582</v>
+        <v>4471</v>
       </c>
       <c r="D3" t="n">
-        <v>28117</v>
+        <v>11968</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1762</v>
+        <v>1039</v>
       </c>
       <c r="C4" t="n">
-        <v>7838</v>
+        <v>7489</v>
       </c>
       <c r="D4" t="n">
-        <v>12437</v>
+        <v>8849</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1279</v>
+        <v>880</v>
       </c>
       <c r="C5" t="n">
-        <v>3515</v>
+        <v>9214</v>
       </c>
       <c r="D5" t="n">
-        <v>3361</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>439</v>
       </c>
       <c r="C6" t="n">
-        <v>2499</v>
+        <v>7359</v>
       </c>
       <c r="D6" t="n">
-        <v>820</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>131</v>
       </c>
       <c r="C7" t="n">
-        <v>1558</v>
+        <v>3191</v>
       </c>
       <c r="D7" t="n">
-        <v>470</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>803</v>
+        <v>886</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" t="n">
         <v>50</v>
-      </c>
-      <c r="D15" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4022</v>
+        <v>227</v>
       </c>
       <c r="C2" t="n">
-        <v>2786</v>
+        <v>5095</v>
       </c>
       <c r="D2" t="n">
-        <v>28959</v>
+        <v>10226</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4262</v>
+        <v>527</v>
       </c>
       <c r="C3" t="n">
-        <v>7434</v>
+        <v>5198</v>
       </c>
       <c r="D3" t="n">
-        <v>28352</v>
+        <v>11441</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2254</v>
+        <v>860</v>
       </c>
       <c r="C4" t="n">
-        <v>9214</v>
+        <v>6245</v>
       </c>
       <c r="D4" t="n">
-        <v>14555</v>
+        <v>9199</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1400</v>
+        <v>912</v>
       </c>
       <c r="C5" t="n">
-        <v>5312</v>
+        <v>8713</v>
       </c>
       <c r="D5" t="n">
-        <v>4368</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>830</v>
+        <v>526</v>
       </c>
       <c r="C6" t="n">
-        <v>2959</v>
+        <v>8272</v>
       </c>
       <c r="D6" t="n">
-        <v>1053</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>1934</v>
+        <v>4511</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1033</v>
+        <v>1380</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3728</v>
+        <v>357</v>
       </c>
       <c r="C2" t="n">
-        <v>5239</v>
+        <v>8787</v>
       </c>
       <c r="D2" t="n">
-        <v>29653</v>
+        <v>14177</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3497</v>
+        <v>349</v>
       </c>
       <c r="C3" t="n">
-        <v>4754</v>
+        <v>4560</v>
       </c>
       <c r="D3" t="n">
-        <v>26529</v>
+        <v>10534</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2662</v>
+        <v>639</v>
       </c>
       <c r="C4" t="n">
-        <v>8185</v>
+        <v>5642</v>
       </c>
       <c r="D4" t="n">
-        <v>16364</v>
+        <v>9263</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1564</v>
+        <v>828</v>
       </c>
       <c r="C5" t="n">
-        <v>6962</v>
+        <v>7549</v>
       </c>
       <c r="D5" t="n">
-        <v>5799</v>
+        <v>4775</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>968</v>
+        <v>618</v>
       </c>
       <c r="C6" t="n">
-        <v>3976</v>
+        <v>8377</v>
       </c>
       <c r="D6" t="n">
-        <v>1516</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>429</v>
+        <v>236</v>
       </c>
       <c r="C7" t="n">
-        <v>2355</v>
+        <v>5983</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1395</v>
+        <v>2558</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>645</v>
+        <v>750</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2265</v>
+        <v>248</v>
       </c>
       <c r="C2" t="n">
-        <v>2536</v>
+        <v>4850</v>
       </c>
       <c r="D2" t="n">
-        <v>20680</v>
+        <v>10435</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3427</v>
+        <v>530</v>
       </c>
       <c r="C3" t="n">
-        <v>4779</v>
+        <v>5987</v>
       </c>
       <c r="D3" t="n">
-        <v>26259</v>
+        <v>11553</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2943</v>
+        <v>1082</v>
       </c>
       <c r="C4" t="n">
-        <v>7746</v>
+        <v>8159</v>
       </c>
       <c r="D4" t="n">
-        <v>17585</v>
+        <v>9459</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1637</v>
+        <v>601</v>
       </c>
       <c r="C5" t="n">
-        <v>8260</v>
+        <v>11476</v>
       </c>
       <c r="D5" t="n">
-        <v>6146</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>781</v>
+        <v>218</v>
       </c>
       <c r="C6" t="n">
-        <v>4675</v>
+        <v>7669</v>
       </c>
       <c r="D6" t="n">
-        <v>1464</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>2480</v>
+        <v>2506</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1042</v>
+        <v>735</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2799</v>
+        <v>166</v>
       </c>
       <c r="C2" t="n">
-        <v>7690</v>
+        <v>3680</v>
       </c>
       <c r="D2" t="n">
-        <v>16077</v>
+        <v>7602</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2546</v>
+        <v>357</v>
       </c>
       <c r="C3" t="n">
-        <v>3405</v>
+        <v>4833</v>
       </c>
       <c r="D3" t="n">
-        <v>23822</v>
+        <v>10589</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2735</v>
+        <v>708</v>
       </c>
       <c r="C4" t="n">
-        <v>6246</v>
+        <v>6733</v>
       </c>
       <c r="D4" t="n">
-        <v>18382</v>
+        <v>9117</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1911</v>
+        <v>557</v>
       </c>
       <c r="C5" t="n">
-        <v>7945</v>
+        <v>8774</v>
       </c>
       <c r="D5" t="n">
-        <v>7606</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>995</v>
+        <v>211</v>
       </c>
       <c r="C6" t="n">
-        <v>6125</v>
+        <v>7610</v>
       </c>
       <c r="D6" t="n">
-        <v>2088</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>49</v>
       </c>
       <c r="C7" t="n">
-        <v>3366</v>
+        <v>3258</v>
       </c>
       <c r="D7" t="n">
-        <v>678</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1555</v>
+        <v>866</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>518</v>
+        <v>260</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1920</v>
+        <v>203</v>
       </c>
       <c r="C2" t="n">
-        <v>4055</v>
+        <v>6913</v>
       </c>
       <c r="D2" t="n">
-        <v>11814</v>
+        <v>13166</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2301</v>
+        <v>228</v>
       </c>
       <c r="C3" t="n">
-        <v>4606</v>
+        <v>3736</v>
       </c>
       <c r="D3" t="n">
-        <v>21696</v>
+        <v>9389</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2469</v>
+        <v>480</v>
       </c>
       <c r="C4" t="n">
-        <v>5145</v>
+        <v>5589</v>
       </c>
       <c r="D4" t="n">
-        <v>18678</v>
+        <v>9108</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2060</v>
+        <v>568</v>
       </c>
       <c r="C5" t="n">
-        <v>7497</v>
+        <v>7553</v>
       </c>
       <c r="D5" t="n">
-        <v>8658</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1136</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>6910</v>
+        <v>8173</v>
       </c>
       <c r="D6" t="n">
-        <v>2528</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>4217</v>
+        <v>5303</v>
       </c>
       <c r="D7" t="n">
-        <v>771</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1970</v>
+        <v>1952</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>570</v>
+        <v>517</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2530</v>
+        <v>388</v>
       </c>
       <c r="C2" t="n">
-        <v>5371</v>
+        <v>20024</v>
       </c>
       <c r="D2" t="n">
-        <v>15554</v>
+        <v>12017</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1831</v>
+        <v>180</v>
       </c>
       <c r="C3" t="n">
-        <v>3959</v>
+        <v>4558</v>
       </c>
       <c r="D3" t="n">
-        <v>19329</v>
+        <v>9271</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2096</v>
+        <v>326</v>
       </c>
       <c r="C4" t="n">
-        <v>4820</v>
+        <v>4583</v>
       </c>
       <c r="D4" t="n">
-        <v>18336</v>
+        <v>8876</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2005</v>
+        <v>488</v>
       </c>
       <c r="C5" t="n">
-        <v>6437</v>
+        <v>6418</v>
       </c>
       <c r="D5" t="n">
-        <v>9741</v>
+        <v>5566</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>390</v>
       </c>
       <c r="C6" t="n">
-        <v>7068</v>
+        <v>7813</v>
       </c>
       <c r="D6" t="n">
-        <v>3260</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>456</v>
+        <v>173</v>
       </c>
       <c r="C7" t="n">
-        <v>5165</v>
+        <v>6566</v>
       </c>
       <c r="D7" t="n">
-        <v>969</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>2717</v>
+        <v>3363</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1014</v>
+        <v>1093</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4756</v>
+        <v>4507</v>
       </c>
       <c r="C2" t="n">
-        <v>8338</v>
+        <v>15352</v>
       </c>
       <c r="D2" t="n">
-        <v>8102</v>
+        <v>13045</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1849</v>
+        <v>447</v>
       </c>
       <c r="C2" t="n">
-        <v>3137</v>
+        <v>16937</v>
       </c>
       <c r="D2" t="n">
-        <v>11573</v>
+        <v>12295</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2438</v>
+        <v>211</v>
       </c>
       <c r="C3" t="n">
-        <v>4618</v>
+        <v>9615</v>
       </c>
       <c r="D3" t="n">
-        <v>20835</v>
+        <v>9007</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2923</v>
+        <v>234</v>
       </c>
       <c r="C4" t="n">
-        <v>7070</v>
+        <v>4476</v>
       </c>
       <c r="D4" t="n">
-        <v>18532</v>
+        <v>8577</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1253</v>
+        <v>393</v>
       </c>
       <c r="C5" t="n">
-        <v>9758</v>
+        <v>5465</v>
       </c>
       <c r="D5" t="n">
-        <v>8642</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="C6" t="n">
-        <v>6308</v>
+        <v>7181</v>
       </c>
       <c r="D6" t="n">
-        <v>2391</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="C7" t="n">
-        <v>2662</v>
+        <v>6987</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>993</v>
+        <v>4585</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>1904</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>582</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6217</v>
+        <v>4694</v>
       </c>
       <c r="C2" t="n">
-        <v>5532</v>
+        <v>11275</v>
       </c>
       <c r="D2" t="n">
-        <v>24611</v>
+        <v>19310</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2022</v>
+        <v>1454</v>
       </c>
       <c r="C3" t="n">
-        <v>4202</v>
+        <v>6062</v>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5557</v>
+        <v>2127</v>
       </c>
       <c r="C2" t="n">
-        <v>5976</v>
+        <v>7415</v>
       </c>
       <c r="D2" t="n">
-        <v>31026</v>
+        <v>25202</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3380</v>
+        <v>2597</v>
       </c>
       <c r="C3" t="n">
-        <v>4272</v>
+        <v>7867</v>
       </c>
       <c r="D3" t="n">
-        <v>5651</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>912</v>
+        <v>698</v>
       </c>
       <c r="C4" t="n">
-        <v>2505</v>
+        <v>3773</v>
       </c>
       <c r="D4" t="n">
-        <v>1584</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6497</v>
+        <v>1785</v>
       </c>
       <c r="C2" t="n">
-        <v>5934</v>
+        <v>10948</v>
       </c>
       <c r="D2" t="n">
-        <v>40294</v>
+        <v>21337</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3647</v>
+        <v>1952</v>
       </c>
       <c r="C3" t="n">
-        <v>4543</v>
+        <v>6623</v>
       </c>
       <c r="D3" t="n">
-        <v>9304</v>
+        <v>8170</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1822</v>
+        <v>1431</v>
       </c>
       <c r="C4" t="n">
-        <v>3412</v>
+        <v>6091</v>
       </c>
       <c r="D4" t="n">
-        <v>2316</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>427</v>
+        <v>339</v>
       </c>
       <c r="C5" t="n">
-        <v>1465</v>
+        <v>2221</v>
       </c>
       <c r="D5" t="n">
-        <v>1220</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5989</v>
+        <v>1912</v>
       </c>
       <c r="C2" t="n">
-        <v>5188</v>
+        <v>10287</v>
       </c>
       <c r="D2" t="n">
-        <v>42185</v>
+        <v>28546</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4068</v>
+        <v>1564</v>
       </c>
       <c r="C3" t="n">
-        <v>4573</v>
+        <v>7750</v>
       </c>
       <c r="D3" t="n">
-        <v>13359</v>
+        <v>9688</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2283</v>
+        <v>1444</v>
       </c>
       <c r="C4" t="n">
-        <v>3905</v>
+        <v>6260</v>
       </c>
       <c r="D4" t="n">
-        <v>3520</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>923</v>
+        <v>745</v>
       </c>
       <c r="C5" t="n">
-        <v>2443</v>
+        <v>4255</v>
       </c>
       <c r="D5" t="n">
-        <v>1360</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>248</v>
+        <v>198</v>
       </c>
       <c r="C6" t="n">
-        <v>880</v>
+        <v>1272</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>823</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5807</v>
+        <v>1848</v>
       </c>
       <c r="C2" t="n">
-        <v>6794</v>
+        <v>7604</v>
       </c>
       <c r="D2" t="n">
-        <v>39275</v>
+        <v>29861</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3619</v>
+        <v>1421</v>
       </c>
       <c r="C3" t="n">
-        <v>4001</v>
+        <v>7866</v>
       </c>
       <c r="D3" t="n">
-        <v>15805</v>
+        <v>11737</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1939</v>
+        <v>1288</v>
       </c>
       <c r="C4" t="n">
-        <v>3461</v>
+        <v>6842</v>
       </c>
       <c r="D4" t="n">
-        <v>4548</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>822</v>
+        <v>940</v>
       </c>
       <c r="C5" t="n">
-        <v>2336</v>
+        <v>5186</v>
       </c>
       <c r="D5" t="n">
-        <v>1359</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>276</v>
+        <v>397</v>
       </c>
       <c r="C6" t="n">
-        <v>1112</v>
+        <v>2718</v>
       </c>
       <c r="D6" t="n">
-        <v>773</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>384</v>
+        <v>764</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4864</v>
+        <v>1824</v>
       </c>
       <c r="C2" t="n">
-        <v>11526</v>
+        <v>12630</v>
       </c>
       <c r="D2" t="n">
-        <v>44039</v>
+        <v>22946</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3895</v>
+        <v>1323</v>
       </c>
       <c r="C3" t="n">
-        <v>4829</v>
+        <v>6878</v>
       </c>
       <c r="D3" t="n">
-        <v>18584</v>
+        <v>13413</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2429</v>
+        <v>1155</v>
       </c>
       <c r="C4" t="n">
-        <v>3710</v>
+        <v>7125</v>
       </c>
       <c r="D4" t="n">
-        <v>6679</v>
+        <v>5342</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1213</v>
+        <v>979</v>
       </c>
       <c r="C5" t="n">
-        <v>2912</v>
+        <v>5857</v>
       </c>
       <c r="D5" t="n">
-        <v>1916</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>507</v>
+        <v>566</v>
       </c>
       <c r="C6" t="n">
-        <v>1791</v>
+        <v>3778</v>
       </c>
       <c r="D6" t="n">
-        <v>874</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>219</v>
       </c>
       <c r="C7" t="n">
-        <v>790</v>
+        <v>1644</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>309</v>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3859</v>
+        <v>1695</v>
       </c>
       <c r="C2" t="n">
-        <v>7077</v>
+        <v>8083</v>
       </c>
       <c r="D2" t="n">
-        <v>40877</v>
+        <v>18375</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3593</v>
+        <v>1874</v>
       </c>
       <c r="C3" t="n">
-        <v>7341</v>
+        <v>11154</v>
       </c>
       <c r="D3" t="n">
-        <v>21144</v>
+        <v>14395</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2710</v>
+        <v>904</v>
       </c>
       <c r="C4" t="n">
-        <v>4209</v>
+        <v>9931</v>
       </c>
       <c r="D4" t="n">
-        <v>8583</v>
+        <v>4934</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1568</v>
+        <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>3280</v>
+        <v>3702</v>
       </c>
       <c r="D5" t="n">
-        <v>2726</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>771</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>2352</v>
+        <v>1611</v>
       </c>
       <c r="D6" t="n">
-        <v>1033</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>1292</v>
+        <v>488</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>549</v>
+        <v>275</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
